--- a/data/catalog/17_proteins_details.xlsx
+++ b/data/catalog/17_proteins_details.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umass-my.sharepoint.com/personal/mtasmin_umass_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd_2022\Computational Biology\resistance_forecast\resistance_forecast\data\catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{76C63C8D-4A99-445B-AFDA-A4184C9E274D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D33DF44A-1421-4FFC-AFC2-8EC0EBF1E5B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3E2460-2069-4637-9B92-72C86EC620BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{88A9DE7E-C7CA-4C39-8D11-8E84FD79BDFE}"/>
+    <workbookView xWindow="37950" yWindow="3975" windowWidth="17280" windowHeight="8880" xr2:uid="{88A9DE7E-C7CA-4C39-8D11-8E84FD79BDFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -401,10 +401,10 @@
     <t>levofloxacin</t>
   </si>
   <si>
-    <t>RV0678_MYCTU</t>
-  </si>
-  <si>
     <t>PEPQ_MYCTU</t>
+  </si>
+  <si>
+    <t>MMPR5_MYCTU</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
         <v>29</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
